--- a/cuadros/MAYO/VICTORIA.xlsx
+++ b/cuadros/MAYO/VICTORIA.xlsx
@@ -1,33 +1,127 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="30">
+  <si>
+    <t>SUCURSAL</t>
+  </si>
+  <si>
+    <t>PROVEEDOR</t>
+  </si>
+  <si>
+    <t>FACTURA</t>
+  </si>
+  <si>
+    <t>FECHA</t>
+  </si>
+  <si>
+    <t>TIPO FISCALIZACIÓN</t>
+  </si>
+  <si>
+    <t>RESPONSABLE</t>
+  </si>
+  <si>
+    <t>INCIDENCIA</t>
+  </si>
+  <si>
+    <t>TIPO DE ERROR</t>
+  </si>
+  <si>
+    <t>OBSERVACIÓN</t>
+  </si>
+  <si>
+    <t>MONTO $</t>
+  </si>
+  <si>
+    <t>F COBRADA</t>
+  </si>
+  <si>
+    <t>CLASIFICACIÓN MONTO</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>VICTORIA</t>
+  </si>
+  <si>
+    <t>ADOLFO'S VICAR, C.A.</t>
+  </si>
+  <si>
+    <t>YEFFERSON MAY MORGADO CHACON</t>
+  </si>
+  <si>
+    <t>124700</t>
+  </si>
+  <si>
+    <t>2026-05-01</t>
+  </si>
+  <si>
+    <t>RECEPCION</t>
+  </si>
+  <si>
+    <t>Ismarlet D. Duran</t>
+  </si>
+  <si>
+    <t>PRODUCTO O SKU DUPLICADO.</t>
+  </si>
+  <si>
+    <t>ERROR DE KG EN TARA.</t>
+  </si>
+  <si>
+    <t>TIPO B</t>
+  </si>
+  <si>
+    <t>TIPO C</t>
+  </si>
+  <si>
+    <t>Duplico dos veces el sku  de  papita colombiana y falto agregar el sku de papa lavada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Falto agregar una cesta de 2.2kg </t>
+  </si>
+  <si>
+    <t>SIN FOTO</t>
+  </si>
+  <si>
+    <t>NINGUNA</t>
+  </si>
+  <si>
+    <t>20260504142228</t>
+  </si>
+  <si>
+    <t>20260504145104</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
   <fonts count="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,80 +140,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -407,84 +434,131 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:N1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>SUCURSAL</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>PROVEEDOR</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>FACTURA</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>FECHA</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>TIPO DE FISCALIZACION</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>RESPONSABLE</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>INCIDENCIA</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>TIPO DE ERROR</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>OBSERVACIONES</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>CLASIFICACION</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>CLASIFICACION</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>F COBRADA</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>CLASIFICACION</t>
-        </is>
+    <row r="1" spans="1:13">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2">
+        <v>13564</v>
+      </c>
+      <c r="D2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2" t="s">
+        <v>26</v>
+      </c>
+      <c r="L2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" t="s">
+        <v>25</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L3" t="s">
+        <v>27</v>
+      </c>
+      <c r="M3" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/cuadros/MAYO/VICTORIA.xlsx
+++ b/cuadros/MAYO/VICTORIA.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="37">
   <si>
     <t>SUCURSAL</t>
   </si>
@@ -64,36 +64,54 @@
     <t>YEFFERSON MAY MORGADO CHACON</t>
   </si>
   <si>
-    <t>124700</t>
+    <t>SUPLIDORA EL VIGIA, COMPAÑIA ANONIMA(SUVICA)</t>
+  </si>
+  <si>
+    <t>004480</t>
   </si>
   <si>
     <t>2026-05-01</t>
   </si>
   <si>
+    <t>2026-05-04</t>
+  </si>
+  <si>
     <t>RECEPCION</t>
   </si>
   <si>
     <t>Ismarlet D. Duran</t>
   </si>
   <si>
+    <t>Yernahil D. Cobo</t>
+  </si>
+  <si>
     <t>PRODUCTO O SKU DUPLICADO.</t>
   </si>
   <si>
     <t>ERROR DE KG EN TARA.</t>
   </si>
   <si>
+    <t>RECEPCIÓN SIN AUTORIZACIÓN DE CMF.</t>
+  </si>
+  <si>
     <t>TIPO B</t>
   </si>
   <si>
     <t>TIPO C</t>
   </si>
   <si>
+    <t>TIPO E</t>
+  </si>
+  <si>
     <t>Duplico dos veces el sku  de  papita colombiana y falto agregar el sku de papa lavada</t>
   </si>
   <si>
     <t xml:space="preserve">Falto agregar una cesta de 2.2kg </t>
   </si>
   <si>
+    <t xml:space="preserve">No envió el documento ante de comenzar la recepción </t>
+  </si>
+  <si>
     <t>SIN FOTO</t>
   </si>
   <si>
@@ -104,6 +122,9 @@
   </si>
   <si>
     <t>20260504145104</t>
+  </si>
+  <si>
+    <t>HIST_20260504160757</t>
   </si>
 </sst>
 </file>
@@ -435,7 +456,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:13">
@@ -490,34 +511,34 @@
         <v>13564</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="L2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="M2" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -527,38 +548,79 @@
       <c r="B3" t="s">
         <v>15</v>
       </c>
-      <c r="C3" t="s">
-        <v>16</v>
+      <c r="C3">
+        <v>124700</v>
       </c>
       <c r="D3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H3" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I3" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J3">
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="L3" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="M3" t="s">
-        <v>29</v>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4" t="s">
+        <v>32</v>
+      </c>
+      <c r="L4" t="s">
+        <v>33</v>
+      </c>
+      <c r="M4" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/cuadros/MAYO/VICTORIA.xlsx
+++ b/cuadros/MAYO/VICTORIA.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="39">
   <si>
     <t>SUCURSAL</t>
   </si>
@@ -55,6 +55,9 @@
     <t>ID</t>
   </si>
   <si>
+    <t>FOTO_INCIDENCIA</t>
+  </si>
+  <si>
     <t>VICTORIA</t>
   </si>
   <si>
@@ -67,7 +70,7 @@
     <t>SUPLIDORA EL VIGIA, COMPAÑIA ANONIMA(SUVICA)</t>
   </si>
   <si>
-    <t>004480</t>
+    <t>4480</t>
   </si>
   <si>
     <t>2026-05-01</t>
@@ -109,7 +112,7 @@
     <t xml:space="preserve">Falto agregar una cesta de 2.2kg </t>
   </si>
   <si>
-    <t xml:space="preserve">No envió el documento ante de comenzar la recepción </t>
+    <t>No pidió la autorización correspondiente para empezar la fiscalización al no enviar el documento del proveedor al CMF</t>
   </si>
   <si>
     <t>SIN FOTO</t>
@@ -125,6 +128,9 @@
   </si>
   <si>
     <t>HIST_20260504160757</t>
+  </si>
+  <si>
+    <t>undefined</t>
   </si>
 </sst>
 </file>
@@ -456,10 +462,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -499,128 +505,134 @@
       <c r="M1" t="s">
         <v>12</v>
       </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2">
         <v>13564</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3">
         <v>124700</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J3">
         <v>0</v>
       </c>
       <c r="K3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L3" t="s">
+        <v>34</v>
+      </c>
+      <c r="M3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4" t="s">
         <v>32</v>
-      </c>
-      <c r="L3" t="s">
-        <v>33</v>
-      </c>
-      <c r="M3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H4" t="s">
-        <v>28</v>
-      </c>
-      <c r="I4" t="s">
-        <v>31</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M4" t="s">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="N4" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/cuadros/MAYO/VICTORIA.xlsx
+++ b/cuadros/MAYO/VICTORIA.xlsx
@@ -1,154 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="39">
-  <si>
-    <t>SUCURSAL</t>
-  </si>
-  <si>
-    <t>PROVEEDOR</t>
-  </si>
-  <si>
-    <t>FACTURA</t>
-  </si>
-  <si>
-    <t>FECHA</t>
-  </si>
-  <si>
-    <t>TIPO FISCALIZACIÓN</t>
-  </si>
-  <si>
-    <t>RESPONSABLE</t>
-  </si>
-  <si>
-    <t>INCIDENCIA</t>
-  </si>
-  <si>
-    <t>TIPO DE ERROR</t>
-  </si>
-  <si>
-    <t>OBSERVACIÓN</t>
-  </si>
-  <si>
-    <t>MONTO $</t>
-  </si>
-  <si>
-    <t>F COBRADA</t>
-  </si>
-  <si>
-    <t>CLASIFICACIÓN MONTO</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>FOTO_INCIDENCIA</t>
-  </si>
-  <si>
-    <t>VICTORIA</t>
-  </si>
-  <si>
-    <t>ADOLFO'S VICAR, C.A.</t>
-  </si>
-  <si>
-    <t>YEFFERSON MAY MORGADO CHACON</t>
-  </si>
-  <si>
-    <t>SUPLIDORA EL VIGIA, COMPAÑIA ANONIMA(SUVICA)</t>
-  </si>
-  <si>
-    <t>4480</t>
-  </si>
-  <si>
-    <t>2026-05-01</t>
-  </si>
-  <si>
-    <t>2026-05-04</t>
-  </si>
-  <si>
-    <t>RECEPCION</t>
-  </si>
-  <si>
-    <t>Ismarlet D. Duran</t>
-  </si>
-  <si>
-    <t>Yernahil D. Cobo</t>
-  </si>
-  <si>
-    <t>PRODUCTO O SKU DUPLICADO.</t>
-  </si>
-  <si>
-    <t>ERROR DE KG EN TARA.</t>
-  </si>
-  <si>
-    <t>RECEPCIÓN SIN AUTORIZACIÓN DE CMF.</t>
-  </si>
-  <si>
-    <t>TIPO B</t>
-  </si>
-  <si>
-    <t>TIPO C</t>
-  </si>
-  <si>
-    <t>TIPO E</t>
-  </si>
-  <si>
-    <t>Duplico dos veces el sku  de  papita colombiana y falto agregar el sku de papa lavada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Falto agregar una cesta de 2.2kg </t>
-  </si>
-  <si>
-    <t>No pidió la autorización correspondiente para empezar la fiscalización al no enviar el documento del proveedor al CMF</t>
-  </si>
-  <si>
-    <t>SIN FOTO</t>
-  </si>
-  <si>
-    <t>NINGUNA</t>
-  </si>
-  <si>
-    <t>20260504142228</t>
-  </si>
-  <si>
-    <t>20260504145104</t>
-  </si>
-  <si>
-    <t>HIST_20260504160757</t>
-  </si>
-  <si>
-    <t>undefined</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -167,13 +46,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -461,178 +407,408 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:14">
-      <c r="A1" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>SUCURSAL</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>PROVEEDOR</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>FACTURA</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>FECHA</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>TIPO FISCALIZACIÓN</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>RESPONSABLE</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>INCIDENCIA</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>TIPO DE ERROR</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>OBSERVACIÓN</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>MONTO $</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>F COBRADA</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>CLASIFICACIÓN MONTO</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>FOTO_INCIDENCIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>VICTORIA</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ADOLFO'S VICAR, C.A.</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>13564</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Ismarlet D. Duran</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>PRODUCTO O SKU DUPLICADO.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>TIPO B</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Duplico dos veces el sku  de  papita colombiana y falto agregar el sku de papa lavada</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" t="s">
-        <v>13</v>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>SIN FOTO</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>20260504142228</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:14">
-      <c r="A2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2">
-        <v>13564</v>
-      </c>
-      <c r="D2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I2" t="s">
-        <v>30</v>
-      </c>
-      <c r="J2">
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>VICTORIA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>YEFFERSON MAY MORGADO CHACON</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>124700</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Ismarlet D. Duran</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ERROR DE KG EN TARA.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>TIPO C</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Falto agregar una cesta de 2.2kg </t>
+        </is>
+      </c>
+      <c r="J3" t="n">
         <v>0</v>
       </c>
-      <c r="K2" t="s">
-        <v>33</v>
-      </c>
-      <c r="L2" t="s">
-        <v>34</v>
-      </c>
-      <c r="M2" t="s">
-        <v>35</v>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>SIN FOTO</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>20260504145104</t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="1:14">
-      <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3">
-        <v>124700</v>
-      </c>
-      <c r="D3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H3" t="s">
-        <v>28</v>
-      </c>
-      <c r="I3" t="s">
-        <v>31</v>
-      </c>
-      <c r="J3">
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>VICTORIA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SUPLIDORA EL VIGIA, COMPAÑIA ANONIMA(SUVICA)</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>4480</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Yernahil D. Cobo</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>RECEPCIÓN SIN AUTORIZACIÓN DE CMF.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>TIPO E</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>No pidió la autorización correspondiente para empezar la fiscalización al no enviar el documento del proveedor al CMF</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
         <v>0</v>
       </c>
-      <c r="K3" t="s">
-        <v>33</v>
-      </c>
-      <c r="L3" t="s">
-        <v>34</v>
-      </c>
-      <c r="M3" t="s">
-        <v>36</v>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>SIN FOTO</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>HIST_20260504160757</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>undefined</t>
+        </is>
       </c>
     </row>
-    <row r="4" spans="1:14">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" t="s">
-        <v>23</v>
-      </c>
-      <c r="G4" t="s">
-        <v>26</v>
-      </c>
-      <c r="H4" t="s">
-        <v>29</v>
-      </c>
-      <c r="I4" t="s">
-        <v>32</v>
-      </c>
-      <c r="J4">
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>VICTORIA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>LA CARIDAD C.A.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>E41774</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Wilrsid I. Villegas</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>ERROR DE KG EN TARA.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>TIPO C</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>colocaron cesta de 3.3kg c/u y eran cestas de 2.3kg c/u</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
         <v>0</v>
       </c>
-      <c r="K4" t="s">
-        <v>33</v>
-      </c>
-      <c r="L4" t="s">
-        <v>34</v>
-      </c>
-      <c r="M4" t="s">
-        <v>37</v>
-      </c>
-      <c r="N4" t="s">
-        <v>38</v>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>ID_20260505141202</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>VICTORIA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CORPORACION SALINERA J.J.D.,S.A</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>53093</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Willvinxton H. Briceño</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>PRODUCTO O SKU DUPLICADO.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>TIPO B</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Coloco varias veces sku sal gruesa </t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>ID_20260506082620</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/cuadros/MAYO/VICTORIA.xlsx
+++ b/cuadros/MAYO/VICTORIA.xlsx
@@ -2,8 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -49,7 +50,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -412,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +550,7 @@
           <t>20260504142228</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -612,6 +614,7 @@
           <t>20260504145104</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -745,6 +748,7 @@
           <t>ID_20260505141202</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -810,6 +814,7 @@
           <t>ID_20260506082620</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -881,7 +886,77 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>VICTORIA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>GRUPO SANT-PANINI,C.A.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>31954</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Ana G. Nieves</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>NO SE COMPLETA EL PROCESO DE FISCALIZACION Y SE ELIMINA.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>TIPO E</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>No se completa el proceso de fiscalización de la cava luxor ya que se dejo liberada y se elimina del aplicativo</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>ID_20260508094616</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>INC_094616.png</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/cuadros/MAYO/VICTORIA.xlsx
+++ b/cuadros/MAYO/VICTORIA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -894,12 +894,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GRUPO SANT-PANINI,C.A.</t>
+          <t>INVERSIONES LAS PATRONAS 2024, C.A.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>31954</t>
+          <t>32069</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -909,12 +909,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RECEPCION</t>
+          <t>DEVOLUCION</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ana G. Nieves</t>
+          <t>Wilrsid I. Villegas</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>No se completa el proceso de fiscalización de la cava luxor ya que se dejo liberada y se elimina del aplicativo</t>
+          <t>No se completa el proceso de fiscalización del proveedor las patronas  ya que se dejo liberada y se elimina del aplicativo</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -947,10 +947,150 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
+          <t>ID_20260508094817</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>INC_094817.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>VICTORIA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>AGROPECUARIA LATIN FRUITS C.A.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>32074</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>DEVOLUCION</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Wilrsid I. Villegas</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>NO SE COMPLETA EL PROCESO DE FISCALIZACION Y SE ELIMINA.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>TIPO E</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>No se completa el proceso de fiscalización del proveedor latín fruits  ya que se dejo liberada y se elimina del aplicativo</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>ID_20260508095028</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>INC_095028.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>VICTORIA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>GRUPO SANT-PANINI,C.A.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>31954</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ana G. Nieves</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>NO SE COMPLETA EL PROCESO DE FISCALIZACION Y SE ELIMINA.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>TIPO E</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>No se completa el proceso de fiscalización del proveedor grupo sant panini  ya que se dejo liberada y se elimina del aplicativo</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
           <t>ID_20260508094616</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>INC_094616.png</t>
         </is>

--- a/cuadros/MAYO/VICTORIA.xlsx
+++ b/cuadros/MAYO/VICTORIA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -550,7 +550,6 @@
           <t>20260504142228</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -614,7 +613,6 @@
           <t>20260504145104</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -748,7 +746,6 @@
           <t>ID_20260505141202</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -814,7 +811,6 @@
           <t>ID_20260506082620</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1049,7 +1045,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RECEPCION</t>
+          <t>DEVOLUCION</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1069,7 +1065,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>No se completa el proceso de fiscalización del proveedor grupo sant panini  ya que se dejo liberada y se elimina del aplicativo</t>
+          <t>No se completa el proceso de fiscalización del proveedor grupo sant panini ya que se dejo liberada y se elimina del aplicativo</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -1087,12 +1083,77 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>ID_20260508094616</t>
+          <t>ID_20260511143027</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>INC_094616.png</t>
+          <t>INC_143027.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>VICTORIA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>INVERSIONES AGROPECUARIA JEANDAVID, C.A.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>019299</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>MARYORI B. GOMEZ</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>RECEPCIÓN SIN AUTORIZACIÓN DE CMF.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>TIPO E</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>no pidió la autorización correspondiente para empezar la fiscalización al no enviar el documento del proveedor al CMF</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>ID_20260511152647</t>
         </is>
       </c>
     </row>

--- a/cuadros/MAYO/VICTORIA.xlsx
+++ b/cuadros/MAYO/VICTORIA.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -50,7 +49,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -413,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -499,8 +498,10 @@
           <t>ADOLFO'S VICAR, C.A.</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>13564</v>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>13564</t>
+        </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -562,8 +563,10 @@
           <t>YEFFERSON MAY MORGADO CHACON</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>124700</v>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>124700</t>
+        </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -625,8 +628,10 @@
           <t>SUPLIDORA EL VIGIA, COMPAÑIA ANONIMA(SUVICA)</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>4480</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>4480</t>
+        </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1157,7 +1162,72 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>VICTORIA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ADOLFO'S VICAR, C.A.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>13662</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>YERNAHIL D. COBO</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>DIFERENCIA ENTRE CANTIDAD FISCALIZADA Y DOCUMENTO.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>TIPO D</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">faltante de 1 kg de espica y 3 kg de zanahoria cancelada por la sucursal </t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>COB_081858_0.jpg COB_081858_1.jpg</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>ID_20260515081858</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/cuadros/MAYO/VICTORIA.xlsx
+++ b/cuadros/MAYO/VICTORIA.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1224,6 +1224,56 @@
       <c r="M12" t="inlineStr">
         <is>
           <t>ID_20260515081858</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>VICTORIA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>CERVECERIA POLAR, C.A.</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>TIPO A</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>ID_20260515164218</t>
         </is>
       </c>
     </row>

--- a/cuadros/MAYO/VICTORIA.xlsx
+++ b/cuadros/MAYO/VICTORIA.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1224,6 +1224,76 @@
       <c r="M12" t="inlineStr">
         <is>
           <t>ID_20260515081858</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>VICTORIA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>CERVECERIA POLAR, C.A.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>3607387262</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Willvinxton H. Briceño</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>OTRAS.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fue cancelada por el proveedor una unidad de cerveza por una mala manipulación </t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>COB_164834_0.jpg</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>ID_20260515164834</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>INC_164834_0.jpg</t>
         </is>
       </c>
     </row>

--- a/cuadros/MAYO/VICTORIA.xlsx
+++ b/cuadros/MAYO/VICTORIA.xlsx
@@ -26,30 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor rgb="FF92D050"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00B0F0"/>
-        <bgColor rgb="FF00B0F0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
-        <bgColor rgb="FFFFC000"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -64,11 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -573,6 +552,7 @@
           <t>20260504142228</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -638,6 +618,7 @@
           <t>20260504145104</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -703,6 +684,7 @@
           <t>HIST_20260504160757</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -768,6 +750,7 @@
           <t>ID_20260506082620</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1113,6 +1096,7 @@
           <t>ID_20260511152647</t>
         </is>
       </c>
+      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1150,6 +1134,7 @@
           <t>OTRAS.</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t xml:space="preserve">fue cancelada por el proveedor una unidad de cerveza por una mala manipulación </t>
@@ -1225,7 +1210,7 @@
           <t>faltante de 1 kg de espica y 3 kg de zanahoria cancelada por la sucursal</t>
         </is>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" t="n">
         <v>8.93</v>
       </c>
       <c r="K12" t="inlineStr">
@@ -1243,6 +1228,7 @@
           <t>ID_20260519104118</t>
         </is>
       </c>
+      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1290,7 +1276,7 @@
           <t>faltante de 200gr de uva roja por no indicar la nota al dorso</t>
         </is>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" t="n">
         <v>1.91</v>
       </c>
       <c r="K13" t="inlineStr">
@@ -1378,6 +1364,7 @@
           <t>ID_20260527131814</t>
         </is>
       </c>
+      <c r="N14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1387,17 +1374,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CENTRAL EL PALMAR, S.A.</t>
+          <t>AGROPECUARIA LATIN FRUITS C.A.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>A91049615</t>
+          <t>006852</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1407,37 +1394,43 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>WILRSID I. VILLEGAS</t>
+          <t>ANA G. NIEVES</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>OTRAS.</t>
+          <t>ERROR DE KG EN TARA.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>TIPO C</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t xml:space="preserve">fue cancelada por el proveedor una unidad de azúcar de 1kg  por llegar averiada en momento del despacho </t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="n">
-        <v>1.59</v>
+          <t>la tara de la guayaba es de 2.4kg y colocaron 2.1kg</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>COB_131823_0.jpeg</t>
+          <t>SIN_FOTO</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>EXCEDENTES</t>
+          <t>NINGUNA</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>ID_20260528131823</t>
-        </is>
-      </c>
+          <t>ID_20260601071843</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1447,17 +1440,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AGROPECUARIA LATIN FRUITS C.A.</t>
+          <t>LA CARIDAD C.A.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>006852</t>
+          <t>E41774</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1467,7 +1460,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ANA G. NIEVES</t>
+          <t>Wilrsid I. Villegas</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1482,11 +1475,11 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>la tara de la guayaba es de 2.4kg y colocaron 2.1kg</t>
+          <t>Se detecto que colocaron 6 cesta de 3.3kg c/u y eran cestas de 2.3kg c/u arrojando una perdida de 12.9kg de molleja de pollo</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>49.02</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1495,14 +1488,15 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>NINGUNA</t>
+          <t>RECUPERACIÓN</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>ID_20260601071843</t>
-        </is>
-      </c>
+          <t>ID_20260505141202</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1512,17 +1506,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>LA CARIDAD C.A.</t>
+          <t>ADOLFO'S VICAR, C.A.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>E41774</t>
+          <t>13741</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1532,7 +1526,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Wilrsid I. Villegas</t>
+          <t>ISMARLET D. DURAN</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1547,11 +1541,11 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Se detecto que colocaron 6 cesta de 3.3kg c/u y eran cestas de 2.3kg c/u arrojando una perdida de 12.9kg de molleja de pollo</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="n">
-        <v>49.02</v>
+          <t xml:space="preserve">la tara de la fresa es de 0.025kg y colocaron 0.250kg arrojando un faltante de 1.12kg </t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>8.16</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1565,7 +1559,12 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>ID_20260505141202</t>
+          <t>ID_20260601075122</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>INC_075122_0.jpeg</t>
         </is>
       </c>
     </row>
@@ -1582,12 +1581,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>13741</t>
+          <t>13803</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1612,11 +1611,11 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t xml:space="preserve">la tara de la fresa es de 0.025kg y colocaron 0.250kg arrojando un faltante de 1.12kg </t>
-        </is>
-      </c>
-      <c r="J18" s="3" t="n">
-        <v>8.16</v>
+          <t>colocaron la tara de la fresa de 0.250kg y era de 0.025kg arrojando un faltante de 2.25kg</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>16.4</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1630,12 +1629,12 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>ID_20260601075122</t>
+          <t>ID_20260601083322</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>INC_075122_0.jpeg</t>
+          <t>INC_083322_0.png</t>
         </is>
       </c>
     </row>
@@ -1647,17 +1646,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ADOLFO'S VICAR, C.A.</t>
+          <t>AGROPECUARIA LO SAMANES</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>13803</t>
+          <t>005277</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1667,26 +1666,26 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ISMARLET D. DURAN</t>
+          <t xml:space="preserve">ORIANA CUBILLO </t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>ERROR DE KG EN TARA.</t>
+          <t>DIFERENCIA ENTRE CANTIDAD FISCALIZADA Y DOCUMENTO.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>TIPO C</t>
+          <t>TIPO D</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>colocaron la tara de la fresa de 0.250kg y era de 0.025kg arrojando un faltante de 2.25kg</t>
-        </is>
-      </c>
-      <c r="J19" s="3" t="n">
-        <v>16.4</v>
+          <t xml:space="preserve">Faltante de 4.4kg de traste por error de transcripción  en el aplicativo Eva , colocaron 338kg y era 333.6kg que recibieron de traste el mismo no fue  cancelado por orden de gerencia  caso abordado por los gerente corporativo </t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>14.12</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1695,17 +1694,17 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>RECUPERACIÓN</t>
+          <t>COBRO</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>ID_20260601083322</t>
+          <t>ID_20260525150603</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>INC_083322_0.png</t>
+          <t>INC_150603_0.jpeg</t>
         </is>
       </c>
     </row>
@@ -1717,17 +1716,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AGROPECUARIA LO SAMANES</t>
+          <t>CENTRAL EL PALMAR, S.A.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>005277</t>
+          <t>A91049615</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1737,47 +1736,39 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORIANA CUBILLO </t>
+          <t xml:space="preserve">proveedor </t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>DIFERENCIA ENTRE CANTIDAD FISCALIZADA Y DOCUMENTO.</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>TIPO D</t>
-        </is>
-      </c>
+          <t>OTRAS.</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Faltante de 4.4kg de traste por error de transcripción  en el aplicativo Eva , colocaron 338kg y era 333.6kg que recibieron de traste el mismo no fue  cancelado por orden de gerencia  caso abordado por los gerente corporativo </t>
-        </is>
-      </c>
-      <c r="J20" s="1" t="n">
-        <v>14.12</v>
+          <t>fue cancelada por el proveedor una unidad de azúcar de 1kg por llegar averiada en momento del despacho</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>SIN_FOTO</t>
+          <t>COB_160000_0.jpeg</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>COBRO</t>
+          <t>NINGUNA</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>ID_20260525150603</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>INC_150603_0.jpeg</t>
-        </is>
-      </c>
+          <t>ID_20260603160000</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cuadros/MAYO/VICTORIA.xlsx
+++ b/cuadros/MAYO/VICTORIA.xlsx
@@ -1106,17 +1106,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CERVECERIA POLAR, C.A.</t>
+          <t>ADOLFO'S VICAR, C.A.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3607387262</t>
+          <t>13662</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1126,43 +1126,43 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Willvinxton H. Briceño</t>
+          <t>YERNAHIL D. COBO</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>OTRAS.</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>DIFERENCIA ENTRE CANTIDAD FISCALIZADA Y DOCUMENTO.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>TIPO D</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve">fue cancelada por el proveedor una unidad de cerveza por una mala manipulación </t>
+          <t>faltante de 1 kg de espica y 3 kg de zanahoria cancelada por la sucursal</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>8.93</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>COB_164834_0.jpg</t>
+          <t>COB_104118_0.jpg COB_104118_1.jpg</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>NINGUNA</t>
+          <t>COBRO</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>ID_20260515164834</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>INC_164834_0.jpg</t>
-        </is>
-      </c>
+          <t>ID_20260519104118</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1172,17 +1172,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ADOLFO'S VICAR, C.A.</t>
+          <t>FRUMIX,C.A.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>13662</t>
+          <t>00009797</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1192,12 +1192,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>YERNAHIL D. COBO</t>
+          <t xml:space="preserve">ISMARLET D. DURAN Y MARIA ALTUVE </t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>DIFERENCIA ENTRE CANTIDAD FISCALIZADA Y DOCUMENTO.</t>
+          <t>NO SE INDICÓ DIFERENCIA AL DORSO DE LA FACTURA.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1207,15 +1207,15 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>faltante de 1 kg de espica y 3 kg de zanahoria cancelada por la sucursal</t>
+          <t>faltante de 200gr de uva roja por no indicar la nota al dorso</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>8.93</v>
+        <v>1.91</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>COB_104118_0.jpg COB_104118_1.jpg</t>
+          <t>COB_092233_0.jpeg</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1225,10 +1225,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>ID_20260519104118</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>ID_20260525143521</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>INC_143521_0.jpeg</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1238,17 +1242,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>FRUMIX,C.A.</t>
+          <t>PROCESADORA DE VEGETALES Y FRUTAS PROVEFRU, C.A.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>00009797</t>
+          <t>021944</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1258,47 +1262,43 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">ISMARLET D. DURAN Y MARIA ALTUVE </t>
+          <t>EDWIN J. AREVALO</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>NO SE INDICÓ DIFERENCIA AL DORSO DE LA FACTURA.</t>
+          <t>RECEPCIÓN SIN AUTORIZACIÓN DE CMF.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>TIPO D</t>
+          <t>TIPO E</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>faltante de 200gr de uva roja por no indicar la nota al dorso</t>
+          <t>no pidió la autorización correspondiente para empezar la fiscalización al no enviar el documento del proveedor al CMF</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>COB_092233_0.jpeg</t>
+          <t>SIN_FOTO</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>COBRO</t>
+          <t>NINGUNA</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>ID_20260525143521</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>INC_143521_0.jpeg</t>
-        </is>
-      </c>
+          <t>ID_20260527131814</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1308,17 +1308,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PROCESADORA DE VEGETALES Y FRUTAS PROVEFRU, C.A.</t>
+          <t>AGROPECUARIA LATIN FRUITS C.A.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>021944</t>
+          <t>006852</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1328,22 +1328,22 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>EDWIN J. AREVALO</t>
+          <t>ANA G. NIEVES</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>RECEPCIÓN SIN AUTORIZACIÓN DE CMF.</t>
+          <t>ERROR DE KG EN TARA.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>TIPO E</t>
+          <t>TIPO C</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>no pidió la autorización correspondiente para empezar la fiscalización al no enviar el documento del proveedor al CMF</t>
+          <t>la tara de la guayaba es de 2.4kg y colocaron 2.1kg</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>ID_20260527131814</t>
+          <t>ID_20260601071843</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1374,17 +1374,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>AGROPECUARIA LATIN FRUITS C.A.</t>
+          <t>LA CARIDAD C.A.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>006852</t>
+          <t>E41774</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ANA G. NIEVES</t>
+          <t>Wilrsid I. Villegas</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1409,11 +1409,11 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>la tara de la guayaba es de 2.4kg y colocaron 2.1kg</t>
+          <t>Se detecto que colocaron 6 cesta de 3.3kg c/u y eran cestas de 2.3kg c/u arrojando una perdida de 12.9kg de molleja de pollo</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>49.02</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1422,12 +1422,12 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>NINGUNA</t>
+          <t>RECUPERACIÓN</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>ID_20260601071843</t>
+          <t>ID_20260505141202</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1440,17 +1440,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LA CARIDAD C.A.</t>
+          <t>ADOLFO'S VICAR, C.A.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>E41774</t>
+          <t>13741</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Wilrsid I. Villegas</t>
+          <t>ISMARLET D. DURAN</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1475,11 +1475,11 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Se detecto que colocaron 6 cesta de 3.3kg c/u y eran cestas de 2.3kg c/u arrojando una perdida de 12.9kg de molleja de pollo</t>
+          <t xml:space="preserve">la tara de la fresa es de 0.025kg y colocaron 0.250kg arrojando un faltante de 1.12kg </t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>49.02</v>
+        <v>8.16</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1493,10 +1493,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>ID_20260505141202</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>ID_20260601075122</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>INC_075122_0.jpeg</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1511,12 +1515,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>13741</t>
+          <t>13803</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1541,11 +1545,11 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve">la tara de la fresa es de 0.025kg y colocaron 0.250kg arrojando un faltante de 1.12kg </t>
+          <t>colocaron la tara de la fresa de 0.250kg y era de 0.025kg arrojando un faltante de 2.25kg</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>8.16</v>
+        <v>16.4</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1559,12 +1563,12 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>ID_20260601075122</t>
+          <t>ID_20260601083322</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>INC_075122_0.jpeg</t>
+          <t>INC_083322_0.png</t>
         </is>
       </c>
     </row>
@@ -1576,17 +1580,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ADOLFO'S VICAR, C.A.</t>
+          <t>AGROPECUARIA LO SAMANES</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>13803</t>
+          <t>005277</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1596,26 +1600,26 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ISMARLET D. DURAN</t>
+          <t xml:space="preserve">ORIANA CUBILLO </t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>ERROR DE KG EN TARA.</t>
+          <t>DIFERENCIA ENTRE CANTIDAD FISCALIZADA Y DOCUMENTO.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>TIPO C</t>
+          <t>TIPO D</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>colocaron la tara de la fresa de 0.250kg y era de 0.025kg arrojando un faltante de 2.25kg</t>
+          <t xml:space="preserve">Faltante de 4.4kg de traste por error de transcripción  en el aplicativo Eva , colocaron 338kg y era 333.6kg que recibieron de traste el mismo no fue  cancelado por orden de gerencia  caso abordado por los gerente corporativo </t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>16.4</v>
+        <v>14.12</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1624,17 +1628,17 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>RECUPERACIÓN</t>
+          <t>COBRO</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>ID_20260601083322</t>
+          <t>ID_20260525150603</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>INC_083322_0.png</t>
+          <t>INC_150603_0.jpeg</t>
         </is>
       </c>
     </row>
@@ -1646,17 +1650,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AGROPECUARIA LO SAMANES</t>
+          <t>CENTRAL EL PALMAR, S.A.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>005277</t>
+          <t>A91049615</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1666,47 +1670,39 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORIANA CUBILLO </t>
+          <t xml:space="preserve">proveedor </t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>DIFERENCIA ENTRE CANTIDAD FISCALIZADA Y DOCUMENTO.</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>TIPO D</t>
-        </is>
-      </c>
+          <t>OTRAS.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Faltante de 4.4kg de traste por error de transcripción  en el aplicativo Eva , colocaron 338kg y era 333.6kg que recibieron de traste el mismo no fue  cancelado por orden de gerencia  caso abordado por los gerente corporativo </t>
+          <t>fue cancelada por el proveedor una unidad de azúcar de 1kg por llegar averiada en momento del despacho</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>14.12</v>
+        <v>0</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>SIN_FOTO</t>
+          <t>COB_160000_0.jpeg</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>COBRO</t>
+          <t>NINGUNA</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>ID_20260525150603</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>INC_150603_0.jpeg</t>
-        </is>
-      </c>
+          <t>ID_20260603160000</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1716,17 +1712,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CENTRAL EL PALMAR, S.A.</t>
+          <t>CERVECERIA POLAR, C.A.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>A91049615</t>
+          <t>3607387262</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1747,7 +1743,7 @@
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>fue cancelada por el proveedor una unidad de azúcar de 1kg por llegar averiada en momento del despacho</t>
+          <t>fue cancelada por el proveedor una unidad de cerveza por una mala manipulación</t>
         </is>
       </c>
       <c r="J20" t="n">
@@ -1755,7 +1751,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>COB_160000_0.jpeg</t>
+          <t>COB_160200_0.jpg</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1765,10 +1761,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>ID_20260603160000</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>ID_20260603160200</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>INC_160200_0.jpg</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cuadros/MAYO/VICTORIA.xlsx
+++ b/cuadros/MAYO/VICTORIA.xlsx
@@ -26,12 +26,24 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor rgb="FF92D050"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor rgb="FFFFC000"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +58,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -552,7 +566,6 @@
           <t>20260504142228</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -618,7 +631,6 @@
           <t>20260504145104</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -684,7 +696,6 @@
           <t>HIST_20260504160757</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -750,7 +761,6 @@
           <t>ID_20260506082620</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1096,7 +1106,6 @@
           <t>ID_20260511152647</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1144,7 +1153,7 @@
           <t>faltante de 1 kg de espica y 3 kg de zanahoria cancelada por la sucursal</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="J11" s="1" t="n">
         <v>8.93</v>
       </c>
       <c r="K11" t="inlineStr">
@@ -1162,7 +1171,6 @@
           <t>ID_20260519104118</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1210,7 +1218,7 @@
           <t>faltante de 200gr de uva roja por no indicar la nota al dorso</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="J12" s="1" t="n">
         <v>1.91</v>
       </c>
       <c r="K12" t="inlineStr">
@@ -1298,7 +1306,6 @@
           <t>ID_20260527131814</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1364,7 +1371,6 @@
           <t>ID_20260601071843</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1412,7 +1418,7 @@
           <t>Se detecto que colocaron 6 cesta de 3.3kg c/u y eran cestas de 2.3kg c/u arrojando una perdida de 12.9kg de molleja de pollo</t>
         </is>
       </c>
-      <c r="J15" t="n">
+      <c r="J15" s="2" t="n">
         <v>49.02</v>
       </c>
       <c r="K15" t="inlineStr">
@@ -1430,7 +1436,6 @@
           <t>ID_20260505141202</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1478,7 +1483,7 @@
           <t xml:space="preserve">la tara de la fresa es de 0.025kg y colocaron 0.250kg arrojando un faltante de 1.12kg </t>
         </is>
       </c>
-      <c r="J16" t="n">
+      <c r="J16" s="2" t="n">
         <v>8.16</v>
       </c>
       <c r="K16" t="inlineStr">
@@ -1548,7 +1553,7 @@
           <t>colocaron la tara de la fresa de 0.250kg y era de 0.025kg arrojando un faltante de 2.25kg</t>
         </is>
       </c>
-      <c r="J17" t="n">
+      <c r="J17" s="2" t="n">
         <v>16.4</v>
       </c>
       <c r="K17" t="inlineStr">
@@ -1618,7 +1623,7 @@
           <t xml:space="preserve">Faltante de 4.4kg de traste por error de transcripción  en el aplicativo Eva , colocaron 338kg y era 333.6kg que recibieron de traste el mismo no fue  cancelado por orden de gerencia  caso abordado por los gerente corporativo </t>
         </is>
       </c>
-      <c r="J18" t="n">
+      <c r="J18" s="1" t="n">
         <v>14.12</v>
       </c>
       <c r="K18" t="inlineStr">
@@ -1678,7 +1683,6 @@
           <t>OTRAS.</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>fue cancelada por el proveedor una unidad de azúcar de 1kg por llegar averiada en momento del despacho</t>
@@ -1702,7 +1706,6 @@
           <t>ID_20260603160000</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1740,7 +1743,6 @@
           <t>OTRAS.</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>fue cancelada por el proveedor una unidad de cerveza por una mala manipulación</t>
